--- a/curation_benchmark/results/supp_tables/supp_table_PR_AUC.xlsx
+++ b/curation_benchmark/results/supp_tables/supp_table_PR_AUC.xlsx
@@ -1,40 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ADRD (80%)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ASD (80%)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ASD_excl_ClinVar (80%)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CHD (80%)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CHD_excl_ClinVar (80%)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DDD (80%)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DDD_excl_ClinVar (80%)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cancer_MSK (80%)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Cancer_TCGA (80%)" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Cancer_AlphaMissense (80%)" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ClinVar_Balanced (80%)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="ClinVar_Onestar+ (80%)" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="ClinVar_Twostar+ (80%)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ClinVar_Threestar+ (80%)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="ADRD (90%)" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="ASD (90%)" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ASD_excl_ClinVar (90%)" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="CHD (90%)" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="CHD_excl_ClinVar (90%)" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="DDD (90%)" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="DDD_excl_ClinVar (90%)" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Cancer_MSK (90%)" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Cancer_TCGA (90%)" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Cancer_AlphaMissense (90%)" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="ClinVar_Balanced (90%)" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="ClinVar_Onestar+ (90%)" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="ClinVar_Twostar+ (90%)" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="ClinVar_Threestar+ (90%)" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADRD (80%)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASD (80%)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASD_excl_ClinVar (80%)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHD (80%)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHD_excl_ClinVar (80%)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDD (80%)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDD_excl_ClinVar (80%)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_MSK (80%)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_TCGA (80%)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_AlphaMissense (80%)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Balanced (80%)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Onestar+ (80%)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Twostar+ (80%)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Threestar+ (80%)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADRD (90%)" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASD (90%)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASD_excl_ClinVar (90%)" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHD (90%)" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHD_excl_ClinVar (90%)" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDD (90%)" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDD_excl_ClinVar (90%)" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_MSK (90%)" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_TCGA (90%)" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_AlphaMissense (90%)" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Balanced (90%)" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Onestar+ (90%)" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Twostar+ (90%)" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Threestar+ (90%)" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,13 +44,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -61,7 +64,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -69,12 +72,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,27 +456,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -1150,27 +1162,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -1852,31 +1864,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -1917,7 +1929,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9695431737337857</v>
+        <v>0.9695431737337855</v>
       </c>
     </row>
     <row r="4">
@@ -2050,7 +2062,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9466584135876203</v>
+        <v>0.9466584135876204</v>
       </c>
     </row>
     <row r="11">
@@ -2069,7 +2081,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9456391391505132</v>
+        <v>0.9456391391505133</v>
       </c>
     </row>
     <row r="12">
@@ -2107,7 +2119,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9376846491379004</v>
+        <v>0.9376846491379006</v>
       </c>
     </row>
     <row r="14">
@@ -2126,7 +2138,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9366326600368289</v>
+        <v>0.9366326600368287</v>
       </c>
     </row>
     <row r="15">
@@ -2145,7 +2157,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9357063324834657</v>
+        <v>0.9357063324834658</v>
       </c>
     </row>
     <row r="16">
@@ -2179,11 +2191,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.92213715515316</v>
+        <v>0.9229937087801453</v>
       </c>
     </row>
     <row r="18">
@@ -2198,11 +2210,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MutationAssessor</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9206228041649548</v>
+        <v>0.92213715515316</v>
       </c>
     </row>
     <row r="19">
@@ -2217,11 +2229,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>MutationAssessor</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9197746821289854</v>
+        <v>0.9206228041649548</v>
       </c>
     </row>
     <row r="20">
@@ -2236,11 +2248,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9170993542932906</v>
+        <v>0.9197746821289854</v>
       </c>
     </row>
     <row r="21">
@@ -2255,11 +2267,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>SIFT4G</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9127254254670276</v>
+        <v>0.9170993542932906</v>
       </c>
     </row>
     <row r="22">
@@ -2274,11 +2286,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9125442086972958</v>
+        <v>0.9127254254670276</v>
       </c>
     </row>
     <row r="23">
@@ -2293,11 +2305,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DEOGEN2</t>
+          <t>Polyphen2_HDIV</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.890941063539642</v>
+        <v>0.9125442086972958</v>
       </c>
     </row>
     <row r="24">
@@ -2312,11 +2324,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.879346422686048</v>
+        <v>0.9064912292559202</v>
       </c>
     </row>
     <row r="25">
@@ -2331,11 +2343,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8724300022467957</v>
+        <v>0.8933028921385335</v>
       </c>
     </row>
     <row r="26">
@@ -2350,11 +2362,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>DEOGEN2</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8631699374844156</v>
+        <v>0.890941063539642</v>
       </c>
     </row>
     <row r="27">
@@ -2369,11 +2381,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>M-CAP</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.8602230864355912</v>
+        <v>0.879346422686048</v>
       </c>
     </row>
     <row r="28">
@@ -2388,11 +2400,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>MetaSVM</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.8592091379411211</v>
+        <v>0.8724300022467957</v>
       </c>
     </row>
     <row r="29">
@@ -2407,11 +2419,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>MetaLR</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.851015184546322</v>
+        <v>0.8631699374844156</v>
       </c>
     </row>
     <row r="30">
@@ -2426,11 +2438,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>M-CAP</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.8184682690005001</v>
+        <v>0.8602230864355911</v>
       </c>
     </row>
     <row r="31">
@@ -2445,11 +2457,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MutFormer</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.811831784374674</v>
+        <v>0.8592091379411211</v>
       </c>
     </row>
     <row r="32">
@@ -2464,10 +2476,67 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>LIST-S2</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.851015184546322</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>24248</v>
+      </c>
+      <c r="B33" t="n">
+        <v>14704</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9544</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PrimateAI</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8184682690005001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>24248</v>
+      </c>
+      <c r="B34" t="n">
+        <v>14704</v>
+      </c>
+      <c r="C34" t="n">
+        <v>9544</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MutFormer</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8118317843746738</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>24248</v>
+      </c>
+      <c r="B35" t="n">
+        <v>14704</v>
+      </c>
+      <c r="C35" t="n">
+        <v>9544</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>DANN</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E35" t="n">
         <v>0.8004631152416826</v>
       </c>
     </row>
@@ -2482,31 +2551,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -2528,7 +2597,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9704758844878805</v>
+        <v>0.9704758844878807</v>
       </c>
     </row>
     <row r="3">
@@ -2566,7 +2635,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9622288072001136</v>
+        <v>0.9622288072001135</v>
       </c>
     </row>
     <row r="5">
@@ -2585,7 +2654,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9594108849298326</v>
+        <v>0.9594108849298328</v>
       </c>
     </row>
     <row r="6">
@@ -2661,7 +2730,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9284555172860577</v>
+        <v>0.9284555172860578</v>
       </c>
     </row>
     <row r="10">
@@ -2680,7 +2749,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9253509975193653</v>
+        <v>0.9253509975193654</v>
       </c>
     </row>
     <row r="11">
@@ -2699,7 +2768,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9168102429326704</v>
+        <v>0.9168102429326703</v>
       </c>
     </row>
     <row r="12">
@@ -2718,7 +2787,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9115191652579737</v>
+        <v>0.9115191652579736</v>
       </c>
     </row>
     <row r="13">
@@ -2756,7 +2825,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9039010269511524</v>
+        <v>0.9039010269511523</v>
       </c>
     </row>
     <row r="15">
@@ -2794,7 +2863,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9024988944646147</v>
+        <v>0.9024988944646148</v>
       </c>
     </row>
     <row r="17">
@@ -2832,7 +2901,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.8855308150630857</v>
+        <v>0.8855308150630856</v>
       </c>
     </row>
     <row r="19">
@@ -2870,7 +2939,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8640931915560879</v>
+        <v>0.8640931915560878</v>
       </c>
     </row>
     <row r="21">
@@ -2908,7 +2977,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8482733131583275</v>
+        <v>0.8482733131583277</v>
       </c>
     </row>
     <row r="23">
@@ -2923,11 +2992,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MutationAssessor</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.8225699719972627</v>
+        <v>0.8331667843541388</v>
       </c>
     </row>
     <row r="24">
@@ -2942,11 +3011,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>MutationAssessor</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.7965805787911845</v>
+        <v>0.8225699719972627</v>
       </c>
     </row>
     <row r="25">
@@ -2961,11 +3030,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.7965147668010311</v>
+        <v>0.8004960046135901</v>
       </c>
     </row>
     <row r="26">
@@ -2980,11 +3049,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.7955668931554568</v>
+        <v>0.7965805787911845</v>
       </c>
     </row>
     <row r="27">
@@ -2999,11 +3068,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.7914763406227106</v>
+        <v>0.7965147668010311</v>
       </c>
     </row>
     <row r="28">
@@ -3018,11 +3087,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.7689519828195505</v>
+        <v>0.7955668931554569</v>
       </c>
     </row>
     <row r="29">
@@ -3037,11 +3106,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.7644445025660936</v>
+        <v>0.7914763406227106</v>
       </c>
     </row>
     <row r="30">
@@ -3056,11 +3125,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.7289827987630397</v>
+        <v>0.774619142023388</v>
       </c>
     </row>
     <row r="31">
@@ -3075,11 +3144,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>Polyphen2_HDIV</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.6874925413136194</v>
+        <v>0.7689519828195505</v>
       </c>
     </row>
     <row r="32">
@@ -3094,11 +3163,68 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>SIFT4G</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7644445025660936</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>85896</v>
+      </c>
+      <c r="B33" t="n">
+        <v>25206</v>
+      </c>
+      <c r="C33" t="n">
+        <v>60690</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LIST-S2</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7289827987630397</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>85896</v>
+      </c>
+      <c r="B34" t="n">
+        <v>25206</v>
+      </c>
+      <c r="C34" t="n">
+        <v>60690</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PrimateAI</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6874925413136194</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>85896</v>
+      </c>
+      <c r="B35" t="n">
+        <v>25206</v>
+      </c>
+      <c r="C35" t="n">
+        <v>60690</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>DANN</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>0.5694466602939156</v>
+      <c r="E35" t="n">
+        <v>0.5694466602939154</v>
       </c>
     </row>
   </sheetData>
@@ -3112,31 +3238,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -3177,7 +3303,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9908756194375845</v>
+        <v>0.9908756194375844</v>
       </c>
     </row>
     <row r="4">
@@ -3196,7 +3322,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9895615719922298</v>
+        <v>0.9895615719922297</v>
       </c>
     </row>
     <row r="5">
@@ -3253,7 +3379,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9701120754056138</v>
+        <v>0.9701120754056136</v>
       </c>
     </row>
     <row r="8">
@@ -3310,7 +3436,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9554183197495265</v>
+        <v>0.9554183197495264</v>
       </c>
     </row>
     <row r="11">
@@ -3386,7 +3512,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.937460737995771</v>
+        <v>0.9374607379957711</v>
       </c>
     </row>
     <row r="15">
@@ -3424,7 +3550,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.931932133846113</v>
+        <v>0.9319321338461131</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3607,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9166298080885471</v>
+        <v>0.9166298080885473</v>
       </c>
     </row>
     <row r="20">
@@ -3500,7 +3626,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9158108733222274</v>
+        <v>0.9158108733222273</v>
       </c>
     </row>
     <row r="21">
@@ -3519,7 +3645,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9056378836725081</v>
+        <v>0.9056378836725083</v>
       </c>
     </row>
     <row r="22">
@@ -3553,11 +3679,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MutationAssessor</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.8714366143339447</v>
+        <v>0.8783867985644396</v>
       </c>
     </row>
     <row r="24">
@@ -3572,11 +3698,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>MutationAssessor</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.8590996304087197</v>
+        <v>0.8714366143339447</v>
       </c>
     </row>
     <row r="25">
@@ -3591,11 +3717,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8559830259808333</v>
+        <v>0.8590996304087197</v>
       </c>
     </row>
     <row r="26">
@@ -3610,11 +3736,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8517815085586257</v>
+        <v>0.8559830259808333</v>
       </c>
     </row>
     <row r="27">
@@ -3629,11 +3755,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.8486118155294219</v>
+        <v>0.8551222488683288</v>
       </c>
     </row>
     <row r="28">
@@ -3648,11 +3774,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.837112505061877</v>
+        <v>0.8517815085586258</v>
       </c>
     </row>
     <row r="29">
@@ -3667,11 +3793,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.8321523580620747</v>
+        <v>0.8510019488035154</v>
       </c>
     </row>
     <row r="30">
@@ -3686,11 +3812,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.8166892374065519</v>
+        <v>0.8486118155294219</v>
       </c>
     </row>
     <row r="31">
@@ -3705,11 +3831,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>Polyphen2_HDIV</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.775502472517885</v>
+        <v>0.837112505061877</v>
       </c>
     </row>
     <row r="32">
@@ -3724,11 +3850,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>SIFT4G</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.751220613847144</v>
+        <v>0.8321523580620747</v>
       </c>
     </row>
     <row r="33">
@@ -3743,11 +3869,68 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>LIST-S2</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8166892374065519</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>25853</v>
+      </c>
+      <c r="B34" t="n">
+        <v>10961</v>
+      </c>
+      <c r="C34" t="n">
+        <v>14892</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PrimateAI</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7755024725178847</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>25853</v>
+      </c>
+      <c r="B35" t="n">
+        <v>10961</v>
+      </c>
+      <c r="C35" t="n">
+        <v>14892</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7512206138471441</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>25853</v>
+      </c>
+      <c r="B36" t="n">
+        <v>10961</v>
+      </c>
+      <c r="C36" t="n">
+        <v>14892</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>DANN</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>0.6967875883608238</v>
+      <c r="E36" t="n">
+        <v>0.6967875883608237</v>
       </c>
     </row>
   </sheetData>
@@ -3761,31 +3944,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -4107,11 +4290,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ESM1b</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9543271304676918</v>
+        <v>0.9569541605403028</v>
       </c>
     </row>
     <row r="19">
@@ -4126,11 +4309,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>ESM1b</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9531851866945218</v>
+        <v>0.9543271304676918</v>
       </c>
     </row>
     <row r="20">
@@ -4145,11 +4328,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9531401746687646</v>
+        <v>0.9537452132488945</v>
       </c>
     </row>
     <row r="21">
@@ -4164,11 +4347,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MutationAssessor</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9503218326583572</v>
+        <v>0.9531851866945218</v>
       </c>
     </row>
     <row r="22">
@@ -4183,11 +4366,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>M-CAP</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9475181651396909</v>
+        <v>0.9531401746687646</v>
       </c>
     </row>
     <row r="23">
@@ -4202,11 +4385,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>MutationAssessor</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9472603991577858</v>
+        <v>0.9503218326583572</v>
       </c>
     </row>
     <row r="24">
@@ -4221,11 +4404,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>M-CAP</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9396076987197935</v>
+        <v>0.9475181651396909</v>
       </c>
     </row>
     <row r="25">
@@ -4240,11 +4423,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>MetaLR</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9377781925280394</v>
+        <v>0.9472603991577858</v>
       </c>
     </row>
     <row r="26">
@@ -4259,11 +4442,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9374306872102373</v>
+        <v>0.9453041415118539</v>
       </c>
     </row>
     <row r="27">
@@ -4278,11 +4461,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9373632043937289</v>
+        <v>0.9396076987197935</v>
       </c>
     </row>
     <row r="28">
@@ -4297,11 +4480,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>Polyphen2_HDIV</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9328909029171804</v>
+        <v>0.9377781925280394</v>
       </c>
     </row>
     <row r="29">
@@ -4316,11 +4499,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>SIFT4G</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9326735694080313</v>
+        <v>0.9374306872102373</v>
       </c>
     </row>
     <row r="30">
@@ -4335,11 +4518,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>MetaSVM</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9221172063272153</v>
+        <v>0.9373632043937289</v>
       </c>
     </row>
     <row r="31">
@@ -4354,11 +4537,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9128973388533146</v>
+        <v>0.9328909029171804</v>
       </c>
     </row>
     <row r="32">
@@ -4373,11 +4556,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MutFormer</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.8754871317688628</v>
+        <v>0.9326735694080313</v>
       </c>
     </row>
     <row r="33">
@@ -4392,11 +4575,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DANN</t>
+          <t>LIST-S2</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.8746272494916514</v>
+        <v>0.9221172063272153</v>
       </c>
     </row>
     <row r="34">
@@ -4411,10 +4594,67 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>PrimateAI</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9128973388533146</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1428</v>
+      </c>
+      <c r="C35" t="n">
+        <v>467</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MutFormer</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8754871317688628</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1428</v>
+      </c>
+      <c r="C36" t="n">
+        <v>467</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DANN</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8746272494916514</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1428</v>
+      </c>
+      <c r="C37" t="n">
+        <v>467</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>MPC</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E37" t="n">
         <v>0.8459560182107804</v>
       </c>
     </row>
@@ -4433,27 +4673,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -4854,27 +5094,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -5522,27 +5762,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -6190,27 +6430,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -6858,27 +7098,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -7526,27 +7766,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -8232,27 +8472,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -8274,7 +8514,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9561353856108735</v>
+        <v>0.9561353856108734</v>
       </c>
     </row>
     <row r="3">
@@ -8293,7 +8533,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9561253462872339</v>
+        <v>0.956125346287234</v>
       </c>
     </row>
     <row r="4">
@@ -8388,7 +8628,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9545250572652043</v>
+        <v>0.9545250572652044</v>
       </c>
     </row>
     <row r="9">
@@ -8426,7 +8666,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.95367745226787</v>
+        <v>0.9536774522678699</v>
       </c>
     </row>
     <row r="11">
@@ -8483,7 +8723,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9530556477281511</v>
+        <v>0.953055647728151</v>
       </c>
     </row>
     <row r="14">
@@ -8502,7 +8742,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9530489391872031</v>
+        <v>0.9530489391872033</v>
       </c>
     </row>
     <row r="15">
@@ -8616,7 +8856,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9520653607831726</v>
+        <v>0.9520653607831725</v>
       </c>
     </row>
     <row r="21">
@@ -8635,7 +8875,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9520105916013988</v>
+        <v>0.9520105916013989</v>
       </c>
     </row>
     <row r="22">
@@ -8673,7 +8913,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9519335498220179</v>
+        <v>0.9519335498220177</v>
       </c>
     </row>
     <row r="24">
@@ -8692,7 +8932,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9516820239648935</v>
+        <v>0.9516820239648937</v>
       </c>
     </row>
     <row r="25">
@@ -8749,7 +8989,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9514386988744797</v>
+        <v>0.9514386988744796</v>
       </c>
     </row>
     <row r="28">
@@ -8900,27 +9140,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -8961,7 +9201,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9492611335127793</v>
+        <v>0.9492611335127792</v>
       </c>
     </row>
     <row r="4">
@@ -8980,7 +9220,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9486788821663459</v>
+        <v>0.9486788821663458</v>
       </c>
     </row>
     <row r="5">
@@ -9075,7 +9315,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9473533482373461</v>
+        <v>0.9473533482373462</v>
       </c>
     </row>
     <row r="10">
@@ -9094,7 +9334,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9472879287577984</v>
+        <v>0.9472879287577983</v>
       </c>
     </row>
     <row r="11">
@@ -9132,7 +9372,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9468472198429965</v>
+        <v>0.9468472198429966</v>
       </c>
     </row>
     <row r="13">
@@ -9189,7 +9429,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9465046348442575</v>
+        <v>0.9465046348442574</v>
       </c>
     </row>
     <row r="16">
@@ -9265,7 +9505,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9462185381585708</v>
+        <v>0.9462185381585709</v>
       </c>
     </row>
     <row r="20">
@@ -9398,7 +9638,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9454333887731694</v>
+        <v>0.9454333887731695</v>
       </c>
     </row>
     <row r="27">
@@ -9568,27 +9808,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -10255,27 +10495,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -10923,27 +11163,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -11606,31 +11846,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -11690,7 +11930,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9536877295336915</v>
+        <v>0.9536877295336916</v>
       </c>
     </row>
     <row r="5">
@@ -11819,11 +12059,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DEOGEN2</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8659428316666852</v>
+        <v>0.8811071306904389</v>
       </c>
     </row>
     <row r="12">
@@ -11838,11 +12078,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
+          <t>DEOGEN2</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8488958629654149</v>
+        <v>0.8659428316666851</v>
       </c>
     </row>
     <row r="13">
@@ -11857,11 +12097,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>MetaSVM</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8413529489722699</v>
+        <v>0.848895862965415</v>
       </c>
     </row>
     <row r="14">
@@ -11876,11 +12116,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>MetaLR</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.83158630039223</v>
+        <v>0.8413529489722698</v>
       </c>
     </row>
     <row r="15">
@@ -11895,11 +12135,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MutFormer</t>
+          <t>LIST-S2</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.7810450714635973</v>
+        <v>0.83158630039223</v>
       </c>
     </row>
     <row r="16">
@@ -11914,10 +12154,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>MutFormer</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7810450714635973</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>35119</v>
+      </c>
+      <c r="B17" t="n">
+        <v>18953</v>
+      </c>
+      <c r="C17" t="n">
+        <v>16166</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>DANN</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E17" t="n">
         <v>0.765662776942842</v>
       </c>
     </row>
@@ -11932,31 +12191,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -11997,7 +12256,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9616748120903604</v>
+        <v>0.9616748120903607</v>
       </c>
     </row>
     <row r="4">
@@ -12016,7 +12275,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9588198683822046</v>
+        <v>0.9588198683822043</v>
       </c>
     </row>
     <row r="5">
@@ -12130,7 +12389,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9016552948902763</v>
+        <v>0.9016552948902762</v>
       </c>
     </row>
     <row r="11">
@@ -12149,7 +12408,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8737980528484862</v>
+        <v>0.873798052848486</v>
       </c>
     </row>
     <row r="12">
@@ -12259,11 +12518,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.7473806306156013</v>
+        <v>0.794110206847454</v>
       </c>
     </row>
     <row r="18">
@@ -12278,11 +12537,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>LIST-S2</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.7152620515363864</v>
+        <v>0.7473806306156013</v>
       </c>
     </row>
     <row r="19">
@@ -12297,11 +12556,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>PrimateAI</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7152620515363863</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124612</v>
+      </c>
+      <c r="B20" t="n">
+        <v>37332</v>
+      </c>
+      <c r="C20" t="n">
+        <v>87280</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>DANN</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>0.5738666860003426</v>
+      <c r="E20" t="n">
+        <v>0.5738666860003427</v>
       </c>
     </row>
   </sheetData>
@@ -12315,31 +12593,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -12361,7 +12639,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9941335123933919</v>
+        <v>0.9941335123933921</v>
       </c>
     </row>
     <row r="3">
@@ -12380,7 +12658,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9901441733290047</v>
+        <v>0.9901441733290046</v>
       </c>
     </row>
     <row r="4">
@@ -12399,7 +12677,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.988747830095116</v>
+        <v>0.9887478300951161</v>
       </c>
     </row>
     <row r="5">
@@ -12513,7 +12791,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9295615687760114</v>
+        <v>0.9295615687760115</v>
       </c>
     </row>
     <row r="11">
@@ -12551,7 +12829,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9123983197618885</v>
+        <v>0.9123983197618886</v>
       </c>
     </row>
     <row r="13">
@@ -12589,7 +12867,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.8997014985134196</v>
+        <v>0.8997014985134197</v>
       </c>
     </row>
     <row r="15">
@@ -12608,7 +12886,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.8805152234641258</v>
+        <v>0.8805152234641257</v>
       </c>
     </row>
     <row r="16">
@@ -12623,11 +12901,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8410065779691263</v>
+        <v>0.8645122235155446</v>
       </c>
     </row>
     <row r="17">
@@ -12642,11 +12920,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8362385125781682</v>
+        <v>0.8410065779691263</v>
       </c>
     </row>
     <row r="18">
@@ -12661,11 +12939,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.8321707155085324</v>
+        <v>0.8397791230065641</v>
       </c>
     </row>
     <row r="19">
@@ -12680,11 +12958,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.8284922149406362</v>
+        <v>0.8362385125781682</v>
       </c>
     </row>
     <row r="20">
@@ -12699,11 +12977,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8093820014673975</v>
+        <v>0.8352920795964897</v>
       </c>
     </row>
     <row r="21">
@@ -12718,11 +12996,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.8038809841358466</v>
+        <v>0.8321707155085324</v>
       </c>
     </row>
     <row r="22">
@@ -12737,11 +13015,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.7950643867057069</v>
+        <v>0.8284922149406362</v>
       </c>
     </row>
     <row r="23">
@@ -12756,11 +13034,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>Polyphen2_HDIV</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.748041593511342</v>
+        <v>0.8093820014673975</v>
       </c>
     </row>
     <row r="24">
@@ -12775,10 +13053,67 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>SIFT4G</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8038809841358466</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>35096</v>
+      </c>
+      <c r="B25" t="n">
+        <v>12592</v>
+      </c>
+      <c r="C25" t="n">
+        <v>22504</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LIST-S2</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7950643867057069</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>35096</v>
+      </c>
+      <c r="B26" t="n">
+        <v>12592</v>
+      </c>
+      <c r="C26" t="n">
+        <v>22504</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PrimateAI</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.748041593511342</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>35096</v>
+      </c>
+      <c r="B27" t="n">
+        <v>12592</v>
+      </c>
+      <c r="C27" t="n">
+        <v>22504</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>DANN</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E27" t="n">
         <v>0.6576339848109907</v>
       </c>
     </row>
@@ -12793,31 +13128,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -13082,11 +13417,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9506709412997902</v>
+        <v>0.9508063748467777</v>
       </c>
     </row>
     <row r="16">
@@ -13101,11 +13436,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MutationAssessor</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9476534624437136</v>
+        <v>0.9506709412997902</v>
       </c>
     </row>
     <row r="17">
@@ -13120,11 +13455,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9450222464509155</v>
+        <v>0.9484431211850102</v>
       </c>
     </row>
     <row r="18">
@@ -13139,11 +13474,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>M-CAP</t>
+          <t>MutationAssessor</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9405080262005721</v>
+        <v>0.9476534624437136</v>
       </c>
     </row>
     <row r="19">
@@ -13158,11 +13493,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>MetaLR</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.937360500783039</v>
+        <v>0.9450222464509155</v>
       </c>
     </row>
     <row r="20">
@@ -13177,11 +13512,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
+          <t>M-CAP</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9347457979451971</v>
+        <v>0.9405080262005721</v>
       </c>
     </row>
     <row r="21">
@@ -13196,11 +13531,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.934496856937695</v>
+        <v>0.9389839210736756</v>
       </c>
     </row>
     <row r="22">
@@ -13215,11 +13550,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9344457172447016</v>
+        <v>0.937360500783039</v>
       </c>
     </row>
     <row r="23">
@@ -13234,11 +13569,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>MetaSVM</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9294906710408916</v>
+        <v>0.9347457979451971</v>
       </c>
     </row>
     <row r="24">
@@ -13253,11 +13588,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>SIFT4G</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9288998094918455</v>
+        <v>0.934496856937695</v>
       </c>
     </row>
     <row r="25">
@@ -13272,11 +13607,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>Polyphen2_HDIV</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9157858575219425</v>
+        <v>0.9344457172447016</v>
       </c>
     </row>
     <row r="26">
@@ -13291,11 +13626,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8821390163439122</v>
+        <v>0.9294906710408916</v>
       </c>
     </row>
     <row r="27">
@@ -13310,11 +13645,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MutFormer</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.8679719057660966</v>
+        <v>0.9288998094918455</v>
       </c>
     </row>
     <row r="28">
@@ -13329,10 +13664,67 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>LIST-S2</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9157858575219425</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1462</v>
+      </c>
+      <c r="C29" t="n">
+        <v>517</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PrimateAI</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8821390163439122</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1462</v>
+      </c>
+      <c r="C30" t="n">
+        <v>517</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MutFormer</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8679719057660966</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1462</v>
+      </c>
+      <c r="C31" t="n">
+        <v>517</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>DANN</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E31" t="n">
         <v>0.86392197859221</v>
       </c>
     </row>
@@ -13351,27 +13743,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -14076,27 +14468,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -14801,27 +15193,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -15526,27 +15918,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -15568,7 +15960,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9585858557473587</v>
+        <v>0.9585858557473588</v>
       </c>
     </row>
     <row r="3">
@@ -15682,7 +16074,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.956212416349782</v>
+        <v>0.9562124163497822</v>
       </c>
     </row>
     <row r="9">
@@ -15777,7 +16169,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9551329132885082</v>
+        <v>0.955132913288508</v>
       </c>
     </row>
     <row r="14">
@@ -15815,7 +16207,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9549477840792873</v>
+        <v>0.9549477840792874</v>
       </c>
     </row>
     <row r="16">
@@ -15853,7 +16245,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9543505751366654</v>
+        <v>0.9543505751366657</v>
       </c>
     </row>
     <row r="18">
@@ -15872,7 +16264,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9543151593002364</v>
+        <v>0.9543151593002362</v>
       </c>
     </row>
     <row r="19">
@@ -15910,7 +16302,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9542883735297452</v>
+        <v>0.9542883735297453</v>
       </c>
     </row>
     <row r="21">
@@ -15967,7 +16359,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.953743401789374</v>
+        <v>0.9537434017893739</v>
       </c>
     </row>
     <row r="24">
@@ -16043,7 +16435,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9532178495754736</v>
+        <v>0.9532178495754737</v>
       </c>
     </row>
     <row r="28">
@@ -16081,7 +16473,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9526244293520707</v>
+        <v>0.9526244293520706</v>
       </c>
     </row>
     <row r="30">
@@ -16119,7 +16511,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9521132778235729</v>
+        <v>0.9521132778235728</v>
       </c>
     </row>
     <row r="32">
@@ -16251,27 +16643,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -16293,7 +16685,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9511419462087474</v>
+        <v>0.9511419462087473</v>
       </c>
     </row>
     <row r="3">
@@ -16312,7 +16704,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9509936961882667</v>
+        <v>0.9509936961882666</v>
       </c>
     </row>
     <row r="4">
@@ -16331,7 +16723,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9509657671803572</v>
+        <v>0.9509657671803571</v>
       </c>
     </row>
     <row r="5">
@@ -16464,7 +16856,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9482462485095358</v>
+        <v>0.9482462485095359</v>
       </c>
     </row>
     <row r="12">
@@ -16521,7 +16913,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9476357404454885</v>
+        <v>0.9476357404454886</v>
       </c>
     </row>
     <row r="15">
@@ -16540,7 +16932,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9474656854091149</v>
+        <v>0.9474656854091148</v>
       </c>
     </row>
     <row r="16">
@@ -16559,7 +16951,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9473212759928163</v>
+        <v>0.9473212759928165</v>
       </c>
     </row>
     <row r="17">
@@ -16578,7 +16970,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9472499861751629</v>
+        <v>0.9472499861751628</v>
       </c>
     </row>
     <row r="18">
@@ -16825,7 +17217,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9452511467553316</v>
+        <v>0.9452511467553315</v>
       </c>
     </row>
     <row r="31">
@@ -16976,27 +17368,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
@@ -17701,27 +18093,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variant_Total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Positive_Labels</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Negative_Labels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auPRC</t>
         </is>
